--- a/template/autofill-template.xlsx
+++ b/template/autofill-template.xlsx
@@ -431,12 +431,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -447,10 +448,15 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Field Name Type</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Field Name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Field Value</t>
         </is>
@@ -464,10 +470,15 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
           <t>first_name | firstname | given-name | First Name</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Jane</t>
         </is>
@@ -481,10 +492,15 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
           <t>last_name | lastname | family-name | Last Name</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Doe</t>
         </is>
@@ -498,10 +514,15 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
           <t>email | email_address | Email</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>jane@example.com</t>
         </is>
@@ -515,26 +536,36 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
           <t>years_experience | yoe | Years of Experience</t>
         </is>
       </c>
-      <c r="C5" s="2" t="n">
+      <c r="D5" s="2" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>number</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>work_authorized | authorized_to_work</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="b">
-        <v>1</v>
+          <t>RegEx</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>expected.*(salary|ctc|compensation)</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>1500000</v>
       </c>
     </row>
     <row r="7">
@@ -545,17 +576,45 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>requires_sponsorship | visa_sponsorship</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="b">
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>work_authorized | authorized_to_work</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>RegEx</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>/require.*sponsor/i</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="b">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="A2:A1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Field Type" error="Pick bool, string or number." type="list">
+  <dataValidations count="2">
+    <dataValidation sqref="A2:A1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Field Type" error="Pick bool, string, number." type="list">
       <formula1>"bool,string,number"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B2:B1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Field Name Type" error="Pick Text, RegEx." type="list">
+      <formula1>"Text,RegEx"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -568,10 +627,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="100" customWidth="1" min="1" max="1"/>
+    <col width="120" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -591,19 +650,40 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Field Name: one or more field names separated by a pipe (|). Spaces around each name are ignored.</t>
+          <t>Field Name Type: Text or RegEx.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Field Value: the value to fill. bool rows hold TRUE or FALSE.</t>
+          <t>Field Name (Text): one or more field names separated by a pipe (|). Spaces around each name are ignored; case and punctuation don't matter.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
+        <is>
+          <t>Field Name (RegEx): one regular expression, tested against the field's name, id, autocomplete and label text. Case-insensitive by default; write /pattern/flags to set flags yourself.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Field Value: the value to fill. bool rows hold TRUE or FALSE.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>If a field matches several rows, the row nearest the top wins.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Keep the Autofill tab first: the extension reads the first tab unless the sheet link has a #gid=.</t>
         </is>
